--- a/src/test/java/gbench/webapps/world/api/model/data/datafile.xlsx
+++ b/src/test/java/gbench/webapps/world/api/model/data/datafile.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26924"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\slicef\ws\gitws\malonylcoa\src\test\java\gbench\webapps\world\api\model\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58ADD865-CA65-455B-A171-830152D33FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA48A41-CCA9-4F74-8119-4416825C3E61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="11640" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="t_maozedong" sheetId="1" r:id="rId1"/>
+    <sheet name="t_wenyan" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1184" uniqueCount="271">
   <si>
     <t>第一次国内革命战争时期</t>
   </si>
@@ -822,6 +823,62 @@
   </si>
   <si>
     <t>中共发言人关于命令国民党反动政府重新逮捕前日本侵华军总司令冈村宁次和逮捕国民党内战罪犯的谈话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TYPE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DESCRIPTION</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名词</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WORD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SUBTYPE</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽象名词</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>德</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>力</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>义</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>智</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>术</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>天下</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>今日</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>具体事物，不占用空间</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5779,4 +5836,156 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FBFA0B0-09A3-4E87-9D3C-50BFACFA9A69}">
+  <dimension ref="B2:F9"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C2" t="s">
+        <v>260</v>
+      </c>
+      <c r="D2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E3" t="s">
+        <v>262</v>
+      </c>
+      <c r="F3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>264</v>
+      </c>
+      <c r="D4" t="s">
+        <v>259</v>
+      </c>
+      <c r="E4" t="s">
+        <v>262</v>
+      </c>
+      <c r="F4" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
+        <v>265</v>
+      </c>
+      <c r="D5" t="s">
+        <v>259</v>
+      </c>
+      <c r="E5" t="s">
+        <v>262</v>
+      </c>
+      <c r="F5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B6">
+        <v>4</v>
+      </c>
+      <c r="C6" t="s">
+        <v>266</v>
+      </c>
+      <c r="D6" t="s">
+        <v>259</v>
+      </c>
+      <c r="E6" t="s">
+        <v>262</v>
+      </c>
+      <c r="F6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B7">
+        <v>5</v>
+      </c>
+      <c r="C7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D7" t="s">
+        <v>259</v>
+      </c>
+      <c r="E7" t="s">
+        <v>262</v>
+      </c>
+      <c r="F7" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" t="s">
+        <v>259</v>
+      </c>
+      <c r="E8" t="s">
+        <v>262</v>
+      </c>
+      <c r="F8" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>269</v>
+      </c>
+      <c r="D9" t="s">
+        <v>259</v>
+      </c>
+      <c r="E9" t="s">
+        <v>262</v>
+      </c>
+      <c r="F9" t="s">
+        <v>270</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>